--- a/rcads/data/xls/82_AgentPersonMap.xlsx
+++ b/rcads/data/xls/82_AgentPersonMap.xlsx
@@ -10,7 +10,7 @@
     <sheet sheetId="1" r:id="rId1" name="_82_AgentPersonMap"/>
   </sheets>
   <definedNames>
-    <definedName name="_82_AgentPersonMap">'_82_AgentPersonMap'!$A$1:$C$149</definedName>
+    <definedName name="_82_AgentPersonMap">'_82_AgentPersonMap'!$A$1:$C$158</definedName>
   </definedNames>
   <calcPr calcId="125725" fullCalcOnLoad="true"/>
 </workbook>
@@ -343,7 +343,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C149"/>
+  <dimension ref="A1:C158"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row outlineLevel="0" r="1">
@@ -1991,6 +1991,105 @@
         <v>112</v>
       </c>
     </row>
+    <row outlineLevel="0" r="150">
+      <c r="A150" s="0">
+        <v>159</v>
+      </c>
+      <c r="B150" s="0">
+        <v>53</v>
+      </c>
+      <c r="C150" s="0">
+        <v>113</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="151">
+      <c r="A151" s="0">
+        <v>160</v>
+      </c>
+      <c r="B151" s="0">
+        <v>53</v>
+      </c>
+      <c r="C151" s="0">
+        <v>114</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="152">
+      <c r="A152" s="0">
+        <v>161</v>
+      </c>
+      <c r="B152" s="0">
+        <v>53</v>
+      </c>
+      <c r="C152" s="0">
+        <v>115</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="153">
+      <c r="A153" s="0">
+        <v>162</v>
+      </c>
+      <c r="B153" s="0">
+        <v>54</v>
+      </c>
+      <c r="C153" s="0">
+        <v>116</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="154">
+      <c r="A154" s="0">
+        <v>163</v>
+      </c>
+      <c r="B154" s="0">
+        <v>54</v>
+      </c>
+      <c r="C154" s="0">
+        <v>117</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="155">
+      <c r="A155" s="0">
+        <v>164</v>
+      </c>
+      <c r="B155" s="0">
+        <v>55</v>
+      </c>
+      <c r="C155" s="0">
+        <v>118</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="156">
+      <c r="A156" s="0">
+        <v>165</v>
+      </c>
+      <c r="B156" s="0">
+        <v>55</v>
+      </c>
+      <c r="C156" s="0">
+        <v>119</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="157">
+      <c r="A157" s="0">
+        <v>166</v>
+      </c>
+      <c r="B157" s="0">
+        <v>55</v>
+      </c>
+      <c r="C157" s="0">
+        <v>120</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="158">
+      <c r="A158" s="0">
+        <v>167</v>
+      </c>
+      <c r="B158" s="0">
+        <v>55</v>
+      </c>
+      <c r="C158" s="0">
+        <v>121</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
